--- a/output/pdf_financials_xlsx/WWA.P.xlsx
+++ b/output/pdf_financials_xlsx/WWA.P.xlsx
@@ -3008,19 +3008,19 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="93">
@@ -4478,7 +4478,11 @@
           <t>Share-based payments reserve 4</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/WWA.P.xlsx
+++ b/output/pdf_financials_xlsx/WWA.P.xlsx
@@ -766,7 +766,7 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.003367</v>
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>-0.079721</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.079721</v>
+        <v>-0.083088</v>
       </c>
       <c r="D27" s="1" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>-0.079721</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.079721</v>
+        <v>-0.083088</v>
       </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
@@ -1483,22 +1483,22 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.245034</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.41295</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.398882</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.393478</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.382471</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.364093</v>
       </c>
     </row>
     <row r="35">
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.245034</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.41295</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.398882</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.393478</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.382471</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.364093</v>
       </c>
     </row>
     <row r="37">
@@ -4198,7 +4198,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -8098,7 +8098,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">

--- a/output/pdf_financials_xlsx/WWA.P.xlsx
+++ b/output/pdf_financials_xlsx/WWA.P.xlsx
@@ -3215,19 +3215,19 @@
         <v>0</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.006121</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>-0.001236</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0</v>
+        <v>0.00693</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0</v>
+        <v>0.000317</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>0</v>
+        <v>-1.5e-05</v>
       </c>
     </row>
     <row r="102">
@@ -3340,19 +3340,19 @@
         <v>-0.002183</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>1e-06</v>
+        <v>-0.00612</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>-0.019813</v>
+        <v>-0.021049</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0.001185</v>
+        <v>0.008115000000000001</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>0.002419</v>
+        <v>0.002736</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>-0.000375</v>
+        <v>-0.00039</v>
       </c>
     </row>
     <row r="107">
@@ -6420,7 +6420,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>-</t>
